--- a/data/input.xlsx
+++ b/data/input.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Номер</t>
   </si>
@@ -73,13 +73,10 @@
     <t>Номенклатура - описание</t>
   </si>
   <si>
-    <t>БезНДС</t>
-  </si>
-  <si>
-    <t>20260608_3</t>
-  </si>
-  <si>
-    <t>20260608_4</t>
+    <t>2026011_1</t>
+  </si>
+  <si>
+    <t>2026011_2</t>
   </si>
 </sst>
 </file>
@@ -585,11 +582,11 @@
       <c r="J2" s="6">
         <v>10500</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="M2" s="9">
         <f t="shared" ref="M2" si="0">I2*J2*5/105</f>
@@ -631,7 +628,7 @@
         <v>0.05</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M3" s="9">
         <f t="shared" ref="M3" si="1">I3*J3*5/105</f>
